--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">

--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">

--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>379</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.2010052170135058</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>369</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.1957016492822788</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>565</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.2996515768143293</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>501</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.2657087433344761</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>552</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.2927569387637341</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>471</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.2497980401407949</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>528</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2800283762087891</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>602</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.3192747774198695</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>473</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2508587536870402</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>558</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2959390794024703</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>445</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.2360087640396045</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>504</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.2672998136538442</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>572</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.3004717698328039</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>526</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.2763079561749212</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>574</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.301522370426625</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>502</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2637007490490692</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>527</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.2768332564718317</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>563</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.2957440671606095</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>537</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.2820862594409366</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>482</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.2531947431108593</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>529</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.2778838570656526</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>506</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2658019502367112</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>446</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.2342839324220815</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>476</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2500429413293963</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>545</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2837360164771596</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>474</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.2467722418535296</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>714</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.3717202124122788</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>502</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.2613495050853837</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>514</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.2675969036133212</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>590</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.307163760956925</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>605</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.3149730091168469</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>535</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.2785298510372117</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>493</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.2566639561894306</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>549</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.2858184826531388</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>547</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.2847772495651492</v>
       </c>
@@ -14624,9 +14519,6 @@
       </c>
       <c r="O72" t="n">
         <v>477</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0.248334091485514</v>

--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">

--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">

--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">

--- a/diseases/d231/2005-2009.xlsx
+++ b/diseases/d231/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
